--- a/02_Zero_Shot/outputs/NLI/DeBERTa-v3-large/RESULT_f-droid_deberta-v3-large_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/DeBERTa-v3-large/RESULT_f-droid_deberta-v3-large_zeroshot.xlsx
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>176.5005554710006</v>
+        <v>231.7362563339993</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06212620748715261</v>
+        <v>0.08156855203590262</v>
       </c>
     </row>
   </sheetData>
